--- a/passenger-data.xlsx
+++ b/passenger-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\source\cs424-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9760970A-2808-4749-8E4A-0898F1822CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3410D41-771A-4FE5-8790-F0CC56D95BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2FAE1D98-6047-4A29-AB5F-53D26DEB9837}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{2FAE1D98-6047-4A29-AB5F-53D26DEB9837}"/>
   </bookViews>
   <sheets>
     <sheet name="Inbound" sheetId="1" r:id="rId1"/>

--- a/passenger-data.xlsx
+++ b/passenger-data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,13 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3410D41-771A-4FE5-8790-F0CC56D95BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{2FAE1D98-6047-4A29-AB5F-53D26DEB9837}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2FAE1D98-6047-4A29-AB5F-53D26DEB9837}"/>
   </bookViews>
   <sheets>
     <sheet name="Inbound" sheetId="1" r:id="rId1"/>
     <sheet name="Outbound" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -558,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC1F3E6-C8EC-473C-90E4-573A033A0184}">
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -1736,6 +1736,1557 @@
         <v>30</v>
       </c>
     </row>
+    <row r="12" spans="1:40">
+      <c r="A12" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>640</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>5</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>4</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>2</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+      <c r="AM12">
+        <v>3</v>
+      </c>
+      <c r="AN12">
+        <f>E12+SUM(F12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12,AB12,AD12,AF12,AH12,AJ12,AL12)-SUM(G12,I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12,AC12,AE12,AG12,AI12,AK12,AM12)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>638</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>6</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>4</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>2</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>5</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>5</v>
+      </c>
+      <c r="AC13">
+        <v>2</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>3</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>2</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>1</v>
+      </c>
+      <c r="AN13">
+        <f>E13+SUM(F13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13,AB13,AD13,AF13,AH13,AJ13,AL13)-SUM(G13,I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13,AC13,AE13,AG13,AI13,AK13,AM13)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40">
+      <c r="A14" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>640</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>8</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>6</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>5</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>5</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>2</v>
+      </c>
+      <c r="AI14">
+        <v>2</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>3</v>
+      </c>
+      <c r="AN14">
+        <f>E14+SUM(F14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14,AB14,AD14,AF14,AH14,AJ14,AL14)-SUM(G14,I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14,AC14,AE14,AG14,AI14,AK14,AM14)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40">
+      <c r="A15" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>638</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>4</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>3</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>4</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>5</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>5</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>2</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>2</v>
+      </c>
+      <c r="AM15">
+        <v>2</v>
+      </c>
+      <c r="AN15">
+        <f>E15+SUM(F15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15,AB15,AD15,AF15,AH15,AJ15,AL15)-SUM(G15,I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15,AC15,AE15,AG15,AI15,AK15,AM15)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
+      <c r="A16" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>640</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E16" s="3">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>9</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>6</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>4</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>3</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>4</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>2</v>
+      </c>
+      <c r="AI16">
+        <v>2</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>3</v>
+      </c>
+      <c r="AN16">
+        <f>E16+SUM(F16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16,AB16,AD16,AF16,AH16,AJ16,AL16)-SUM(G16,I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16,AC16,AE16,AG16,AI16,AK16,AM16)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40">
+      <c r="A17" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>640</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>8</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>5</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>5</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>3</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>2</v>
+      </c>
+      <c r="AN17">
+        <f>E17+SUM(F17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17,AB17,AD17,AF17,AH17,AJ17,AL17)-SUM(G17,I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17,AC17,AE17,AG17,AI17,AK17,AM17)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40">
+      <c r="A18" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>638</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>6</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>4</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>3</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>3</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>3</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>6</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>3</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>2</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>1</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>2</v>
+      </c>
+      <c r="AN18">
+        <f>E18+SUM(F18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18,AB18,AD18,AF18,AH18,AJ18,AL18)-SUM(G18,I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18,AC18,AE18,AG18,AI18,AK18,AM18)</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40">
+      <c r="A19" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>640</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>10</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>4</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>5</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>3</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>2</v>
+      </c>
+      <c r="AL19">
+        <v>2</v>
+      </c>
+      <c r="AM19">
+        <v>4</v>
+      </c>
+      <c r="AN19">
+        <f>E19+SUM(F19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19,AB19,AD19,AF19,AH19,AJ19,AL19)-SUM(G19,I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19,AC19,AE19,AG19,AI19,AK19,AM19)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40">
+      <c r="A20" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>638</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>5</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>2</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>3</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>8</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>3</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>3</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>2</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>2</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>4</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>3</v>
+      </c>
+      <c r="AM20">
+        <v>3</v>
+      </c>
+      <c r="AN20">
+        <f>E20+SUM(F20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20,AB20,AD20,AF20,AH20,AJ20,AL20)-SUM(G20,I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20,AC20,AE20,AG20,AI20,AK20,AM20)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40">
+      <c r="A21" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>640</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>9</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>7</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>3</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>2</v>
+      </c>
+      <c r="AN21">
+        <f>E21+SUM(F21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21,AB21,AD21,AF21,AH21,AJ21,AL21)-SUM(G21,I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21,AC21,AE21,AG21,AI21,AK21,AM21)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40">
+      <c r="A22" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>640</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E22" s="3">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>8</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>7</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>3</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>4</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>2</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+      <c r="AM22">
+        <v>3</v>
+      </c>
+      <c r="AN22">
+        <f>E22+SUM(F22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22,AB22,AD22,AF22,AH22,AJ22,AL22)-SUM(G22,I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22,AC22,AE22,AG22,AI22,AK22,AM22)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40">
+      <c r="A23" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>638</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>4</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>4</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+      <c r="X23">
+        <v>5</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>5</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>5</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>4</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>2</v>
+      </c>
+      <c r="AM23">
+        <v>1</v>
+      </c>
+      <c r="AN23">
+        <f>E23+SUM(F23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23,AB23,AD23,AF23,AH23,AJ23,AL23)-SUM(G23,I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23,AC23,AE23,AG23,AI23,AK23,AM23)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40">
+      <c r="A24" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>640</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E24" s="3">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>7</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>7</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>2</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>4</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>1</v>
+      </c>
+      <c r="AI24">
+        <v>2</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>4</v>
+      </c>
+      <c r="AN24">
+        <f>E24+SUM(F24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24,AB24,AD24,AF24,AH24,AJ24,AL24)-SUM(G24,I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24,AC24,AE24,AG24,AI24,AK24,AM24)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40">
+      <c r="A25" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>638</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>8</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>5</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>2</v>
+      </c>
+      <c r="X25">
+        <v>5</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>4</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>6</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>2</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>2</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>4</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>2</v>
+      </c>
+      <c r="AM25">
+        <v>2</v>
+      </c>
+      <c r="AN25">
+        <f>E25+SUM(F25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25,AB25,AD25,AF25,AH25,AJ25,AL25)-SUM(G25,I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25,AC25,AE25,AG25,AI25,AK25,AM25)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40">
+      <c r="A26" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>640</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="E26" s="3">
+        <v>7</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>10</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>6</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>4</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>2</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>5</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>1</v>
+      </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>2</v>
+      </c>
+      <c r="AN26">
+        <f>E26+SUM(F26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26,AB26,AD26,AF26,AH26,AJ26,AL26)-SUM(G26,I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26,AC26,AE26,AG26,AI26,AK26,AM26)</f>
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1743,7 +3294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E898022C-4238-4BB3-B48F-BCC10379F819}">
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -2756,6 +4307,1305 @@
         <v>4</v>
       </c>
     </row>
+    <row r="12" spans="1:40">
+      <c r="A12" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>627</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E12">
+        <f>AN12+SUM(G12,I12,K12,M12,O12,Q12,S12,U12,W12,Y12,AA12,AC12,AE12,AG12,AI12,AK12,AM12)-SUM(F12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12,AB12,AD12,AF12,AH12,AJ12,AL12)</f>
+        <v>39</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>3</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>4</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>4</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>2</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>7</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>4</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>2</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>5</v>
+      </c>
+      <c r="AN12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>655</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="E13">
+        <f>AN13+SUM(G13,I13,K13,M13,O13,Q13,S13,U13,W13,Y13,AA13,AC13,AE13,AG13,AI13,AK13,AM13)-SUM(F13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13,AB13,AD13,AF13,AH13,AJ13,AL13)</f>
+        <v>39</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>15</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>11</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>4</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>5</v>
+      </c>
+      <c r="AN13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40">
+      <c r="A14" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>627</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E14">
+        <f>AN14+SUM(G14,I14,K14,M14,O14,Q14,S14,U14,W14,Y14,AA14,AC14,AE14,AG14,AI14,AK14,AM14)-SUM(F14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14,AB14,AD14,AF14,AH14,AJ14,AL14)</f>
+        <v>26</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>2</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>2</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>4</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>6</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>5</v>
+      </c>
+      <c r="AN14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40">
+      <c r="A15" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>655</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="E15">
+        <f>AN15+SUM(G15,I15,K15,M15,O15,Q15,S15,U15,W15,Y15,AA15,AC15,AE15,AG15,AI15,AK15,AM15)-SUM(F15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15,AB15,AD15,AF15,AH15,AJ15,AL15)</f>
+        <v>36</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>14</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>7</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>5</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>8</v>
+      </c>
+      <c r="AN15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
+      <c r="A16" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>627</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E16">
+        <f>AN16+SUM(G16,I16,K16,M16,O16,Q16,S16,U16,W16,Y16,AA16,AC16,AE16,AG16,AI16,AK16,AM16)-SUM(F16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16,AB16,AD16,AF16,AH16,AJ16,AL16)</f>
+        <v>31</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>3</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>2</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>4</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>5</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>7</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>2</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>2</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>3</v>
+      </c>
+      <c r="AN16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40">
+      <c r="A17" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>627</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E17">
+        <f>AN17+SUM(G17,I17,K17,M17,O17,Q17,S17,U17,W17,Y17,AA17,AC17,AE17,AG17,AI17,AK17,AM17)-SUM(F17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17,AB17,AD17,AF17,AH17,AJ17,AL17)</f>
+        <v>25</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>4</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>2</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>9</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>3</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>3</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>2</v>
+      </c>
+      <c r="AN17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40">
+      <c r="A18" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>655</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="E18">
+        <f>AN18+SUM(G18,I18,K18,M18,O18,Q18,S18,U18,W18,Y18,AA18,AC18,AE18,AG18,AI18,AK18,AM18)-SUM(F18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18,AB18,AD18,AF18,AH18,AJ18,AL18)</f>
+        <v>40</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>15</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>10</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>7</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>6</v>
+      </c>
+      <c r="AN18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40">
+      <c r="A19" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>627</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E19">
+        <f>AN19+SUM(G19,I19,K19,M19,O19,Q19,S19,U19,W19,Y19,AA19,AC19,AE19,AG19,AI19,AK19,AM19)-SUM(F19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19,AB19,AD19,AF19,AH19,AJ19,AL19)</f>
+        <v>22</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>3</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>3</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>7</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>4</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>3</v>
+      </c>
+      <c r="AN19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40">
+      <c r="A20" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>655</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="E20">
+        <f>AN20+SUM(G20,I20,K20,M20,O20,Q20,S20,U20,W20,Y20,AA20,AC20,AE20,AG20,AI20,AK20,AM20)-SUM(F20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20,AB20,AD20,AF20,AH20,AJ20,AL20)</f>
+        <v>43</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>15</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>10</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>7</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>8</v>
+      </c>
+      <c r="AN20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40">
+      <c r="A21" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>627</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E21">
+        <f>AN21+SUM(G21,I21,K21,M21,O21,Q21,S21,U21,W21,Y21,AA21,AC21,AE21,AG21,AI21,AK21,AM21)-SUM(F21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21,AB21,AD21,AF21,AH21,AJ21,AL21)</f>
+        <v>25</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>3</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>3</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>5</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>6</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>2</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>3</v>
+      </c>
+      <c r="AN21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40">
+      <c r="A22" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>627</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E22">
+        <f>AN22+SUM(G22,I22,K22,M22,O22,Q22,S22,U22,W22,Y22,AA22,AC22,AE22,AG22,AI22,AK22,AM22)-SUM(F22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22,AB22,AD22,AF22,AH22,AJ22,AL22)</f>
+        <v>22</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>2</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>4</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>4</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>5</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>7</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>2</v>
+      </c>
+      <c r="AN22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40">
+      <c r="A23" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>655</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="E23">
+        <f>AN23+SUM(G23,I23,K23,M23,O23,Q23,S23,U23,W23,Y23,AA23,AC23,AE23,AG23,AI23,AK23,AM23)-SUM(F23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23,AB23,AD23,AF23,AH23,AJ23,AL23)</f>
+        <v>44</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>15</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>10</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>9</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>8</v>
+      </c>
+      <c r="AN23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40">
+      <c r="A24" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>627</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E24">
+        <f>AN24+SUM(G24,I24,K24,M24,O24,Q24,S24,U24,W24,Y24,AA24,AC24,AE24,AG24,AI24,AK24,AM24)-SUM(F24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24,AB24,AD24,AF24,AH24,AJ24,AL24)</f>
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>2</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>4</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>7</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>7</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>3</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>2</v>
+      </c>
+      <c r="AN24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40">
+      <c r="A25" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>655</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.71875</v>
+      </c>
+      <c r="E25">
+        <f>AN25+SUM(G25,I25,K25,M25,O25,Q25,S25,U25,W25,Y25,AA25,AC25,AE25,AG25,AI25,AK25,AM25)-SUM(F25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25,AB25,AD25,AF25,AH25,AJ25,AL25)</f>
+        <v>48</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>19</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>12</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>8</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>6</v>
+      </c>
+      <c r="AN25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40">
+      <c r="A26" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>627</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.5243055555555556</v>
+      </c>
+      <c r="E26">
+        <f>AN26+SUM(G26,I26,K26,M26,O26,Q26,S26,U26,W26,Y26,AA26,AC26,AE26,AG26,AI26,AK26,AM26)-SUM(F26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26,AB26,AD26,AF26,AH26,AJ26,AL26)</f>
+        <v>29</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>2</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>2</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>2</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>4</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>5</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>5</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>4</v>
+      </c>
+      <c r="AN26">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
